--- a/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -32,8 +32,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="D18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+测试Y重排序到Z前面</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="144">
   <si>
     <t>普通表模板</t>
   </si>
@@ -498,18 +530,27 @@
     <t>字符串配置在一起的时候，特殊字符串要加引号</t>
   </si>
   <si>
+    <t>测试多态数据修正</t>
+  </si>
+  <si>
     <t>C/S {intern: true}</t>
   </si>
   <si>
     <t>double</t>
   </si>
   <si>
+    <t>Object</t>
+  </si>
+  <si>
     <t>rate</t>
   </si>
   <si>
     <t>rate2</t>
   </si>
   <si>
+    <t>v3orV4</t>
+  </si>
+  <si>
     <t>list1</t>
   </si>
   <si>
@@ -528,6 +569,9 @@
     <t>概率-会被导出为科学计数法</t>
   </si>
   <si>
+    <t>测试自定义结构数据修正</t>
+  </si>
+  <si>
     <t>测试字符串池化</t>
   </si>
   <si>
@@ -540,16 +584,25 @@
     <t>大A今天3400点，明天怎么走？</t>
   </si>
   <si>
+    <t>{@{DV3} x: 0, y: 0,  z: 0}</t>
+  </si>
+  <si>
     <t>大A今天3401点，明天怎么走？</t>
   </si>
   <si>
     <t>大A今天3402点，明天怎么走？</t>
   </si>
   <si>
+    <t>{@{DV3} x: 1, z: 1, y: 1}</t>
+  </si>
+  <si>
     <t>大A今天3403点，明天怎么走？</t>
   </si>
   <si>
     <t>大A今天3404点，明天怎么走？</t>
+  </si>
+  <si>
+    <t>{@{DV4} x: 1, y: 0, z : 1}</t>
   </si>
   <si>
     <t>大A今天3405点，明天怎么走？</t>
@@ -577,7 +630,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,6 +788,17 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1186,7 +1250,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1198,6 +1262,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2382,7 +2449,7 @@
       <c r="H15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>94</v>
       </c>
       <c r="J15" s="2"/>
@@ -2690,32 +2757,38 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:G24"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A4:H24"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="1"/>
     <col min="2" max="2" width="27" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.4444444444444" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="7" width="29" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88888888888889" style="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.4444444444444" style="1" customWidth="1"/>
+    <col min="7" max="8" width="29" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:5">
-      <c r="D4" s="1" t="s">
+    <row r="4" spans="5:6">
+      <c r="E4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="4:4">
-      <c r="D5" s="1" t="s">
+    <row r="5" spans="5:5">
+      <c r="E5" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="11" ht="15.6" spans="1:7">
+    <row r="7" spans="4:4">
+      <c r="D7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" ht="15.6" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2726,100 +2799,112 @@
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:7">
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:8">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="G12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:7">
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:8">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" ht="15.6" spans="1:7">
+        <v>123</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" ht="15.6" spans="1:8">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" ht="15.6" spans="1:7">
+        <v>128</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" ht="15.6" spans="1:8">
       <c r="A15" s="2">
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>127</v>
+      <c r="E15" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" ht="15.6" spans="1:7">
+        <v>131</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:8">
       <c r="A16" s="2">
         <v>10002</v>
       </c>
@@ -2829,17 +2914,20 @@
       <c r="C16" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>128</v>
+      <c r="D16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" ht="15.6" spans="1:7">
+        <v>133</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" ht="15.6" spans="1:8">
       <c r="A17" s="2">
         <v>10003</v>
       </c>
@@ -2849,17 +2937,18 @@
       <c r="C17" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>129</v>
+      <c r="D17" s="2"/>
+      <c r="E17" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" ht="15.6" spans="1:7">
+        <v>134</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" ht="15.6" spans="1:8">
       <c r="A18" s="2">
         <v>10004</v>
       </c>
@@ -2869,17 +2958,20 @@
       <c r="C18" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="D18" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>130</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" ht="15.6" spans="1:7">
+        <v>136</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" ht="15.6" spans="1:8">
       <c r="A19" s="2">
         <v>10005</v>
       </c>
@@ -2889,17 +2981,17 @@
       <c r="C19" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>131</v>
+      <c r="E19" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" ht="15.6" spans="1:7">
+        <v>137</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" ht="15.6" spans="1:8">
       <c r="A20" s="2">
         <v>10006</v>
       </c>
@@ -2909,17 +3001,20 @@
       <c r="C20" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>132</v>
+      <c r="D20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" ht="15.6" spans="1:7">
+        <v>139</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" ht="15.6" spans="1:8">
       <c r="A21" s="2">
         <v>10007</v>
       </c>
@@ -2929,17 +3024,18 @@
       <c r="C21" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>133</v>
+      <c r="D21" s="2"/>
+      <c r="E21" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" ht="15.6" spans="1:7">
+        <v>140</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" ht="15.6" spans="1:8">
       <c r="A22" s="2">
         <v>10008</v>
       </c>
@@ -2949,17 +3045,17 @@
       <c r="C22" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>134</v>
+      <c r="E22" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" ht="15.6" spans="1:7">
+        <v>141</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" ht="15.6" spans="1:8">
       <c r="A23" s="2">
         <v>10009</v>
       </c>
@@ -2969,17 +3065,18 @@
       <c r="C23" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>135</v>
+      <c r="D23" s="2"/>
+      <c r="E23" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" ht="15.6" spans="1:7">
+        <v>142</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" ht="15.6" spans="1:8">
       <c r="A24" s="2">
         <v>10010</v>
       </c>
@@ -2989,18 +3086,20 @@
       <c r="C24" s="2">
         <v>1e-5</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>136</v>
+      <c r="D24" s="2"/>
+      <c r="E24" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="141">
   <si>
     <t>普通表模板</t>
   </si>
@@ -530,48 +530,45 @@
     <t>字符串配置在一起的时候，特殊字符串要加引号</t>
   </si>
   <si>
+    <t>C/S {intern: true}</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>rate2</t>
+  </si>
+  <si>
+    <t>v3orV4</t>
+  </si>
+  <si>
+    <t>list1</t>
+  </si>
+  <si>
+    <t>list2</t>
+  </si>
+  <si>
+    <t>list2#1</t>
+  </si>
+  <si>
+    <t>list2#2</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <t>概率-会被导出为科学计数法</t>
+  </si>
+  <si>
     <t>测试多态数据修正</t>
   </si>
   <si>
-    <t>C/S {intern: true}</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>Object</t>
-  </si>
-  <si>
-    <t>rate</t>
-  </si>
-  <si>
-    <t>rate2</t>
-  </si>
-  <si>
-    <t>v3orV4</t>
-  </si>
-  <si>
-    <t>list1</t>
-  </si>
-  <si>
-    <t>list2</t>
-  </si>
-  <si>
-    <t>list2#1</t>
-  </si>
-  <si>
-    <t>list2#2</t>
-  </si>
-  <si>
-    <t>概率</t>
-  </si>
-  <si>
-    <t>概率-会被导出为科学计数法</t>
-  </si>
-  <si>
-    <t>测试自定义结构数据修正</t>
-  </si>
-  <si>
     <t>测试字符串池化</t>
   </si>
   <si>
@@ -581,43 +578,37 @@
     <t>[abc, "123"]</t>
   </si>
   <si>
-    <t>大A今天3400点，明天怎么走？</t>
-  </si>
-  <si>
     <t>{@{DV3} x: 0, y: 0,  z: 0}</t>
   </si>
   <si>
-    <t>大A今天3401点，明天怎么走？</t>
-  </si>
-  <si>
-    <t>大A今天3402点，明天怎么走？</t>
+    <t>ani_30003</t>
   </si>
   <si>
     <t>{@{DV3} x: 1, z: 1, y: 1}</t>
   </si>
   <si>
-    <t>大A今天3403点，明天怎么走？</t>
-  </si>
-  <si>
-    <t>大A今天3404点，明天怎么走？</t>
+    <t>ani_30004</t>
+  </si>
+  <si>
+    <t>ani_30005</t>
   </si>
   <si>
     <t>{@{DV4} x: 1, y: 0, z : 1}</t>
   </si>
   <si>
-    <t>大A今天3405点，明天怎么走？</t>
-  </si>
-  <si>
-    <t>大A今天3406点，明天怎么走？</t>
-  </si>
-  <si>
-    <t>大A今天3407点，明天怎么走？</t>
-  </si>
-  <si>
-    <t>大A今天3408点，明天怎么走？</t>
-  </si>
-  <si>
-    <t>大A今天3409点，明天怎么走？</t>
+    <t>ani_30006</t>
+  </si>
+  <si>
+    <t>ani_30007</t>
+  </si>
+  <si>
+    <t>ani_30008</t>
+  </si>
+  <si>
+    <t>ani_30009</t>
+  </si>
+  <si>
+    <t>ani_30010</t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1241,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1262,9 +1253,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2449,7 +2437,7 @@
       <c r="H15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>94</v>
       </c>
       <c r="J15" s="2"/>
@@ -2783,11 +2771,6 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="4:4">
-      <c r="D7" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
     <row r="11" ht="15.6" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>2</v>
@@ -2802,10 +2785,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2815,13 +2798,13 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>67</v>
@@ -2837,25 +2820,25 @@
         <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:8">
@@ -2863,25 +2846,25 @@
         <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:8">
@@ -2889,19 +2872,19 @@
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:8">
@@ -2915,16 +2898,16 @@
         <v>1e-5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:8">
@@ -2939,13 +2922,13 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="18" ht="15.6" spans="1:8">
@@ -2959,16 +2942,16 @@
         <v>1e-5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="19" ht="15.6" spans="1:8">
@@ -2982,13 +2965,13 @@
         <v>1e-5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:8">
@@ -3002,16 +2985,16 @@
         <v>1e-5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="21" ht="15.6" spans="1:8">
@@ -3026,13 +3009,13 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="22" ht="15.6" spans="1:8">
@@ -3046,13 +3029,13 @@
         <v>1e-5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="23" ht="15.6" spans="1:8">
@@ -3067,13 +3050,13 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="24" ht="15.6" spans="1:8">
@@ -3088,13 +3071,13 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>143</v>
+        <v>129</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="141">
   <si>
     <t>普通表模板</t>
   </si>
@@ -302,7 +302,7 @@
     <t>Element列可以不配置类型</t>
   </si>
   <si>
-    <t>C {isRecord: true}</t>
+    <t>C {isTuple: true}</t>
   </si>
   <si>
     <r>
@@ -2487,92 +2487,97 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
     <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.22222222222222" customWidth="1"/>
-    <col min="7" max="7" width="11.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.22222222222222" customWidth="1"/>
+    <col min="11" max="11" width="11.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="4" ht="15.6" spans="6:13">
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="10:17">
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="15.6" spans="6:13">
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="10:17">
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="15.6" spans="6:13">
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="10:17">
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="15.6" spans="6:13">
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="10:17">
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="15.6" spans="6:13">
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" ht="15.6" spans="10:17">
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="15.6" spans="6:13">
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="10:17">
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="15.6" spans="6:13">
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="10:17">
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:13">
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:17">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2587,19 +2592,31 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:13">
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:17">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -2616,19 +2633,31 @@
         <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:13">
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:17">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -2645,19 +2674,31 @@
         <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:13">
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:17">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
@@ -2674,19 +2715,31 @@
         <v>84</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="15.6" spans="1:10">
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:14">
       <c r="A15" s="2">
         <v>11001</v>
       </c>
@@ -2702,17 +2755,21 @@
       <c r="E15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="2">
         <v>10</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" ht="15.6" spans="1:10">
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:14">
       <c r="A16" s="2">
         <v>11002</v>
       </c>
@@ -2726,15 +2783,19 @@
         <v>110</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="2">
-        <v>20</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="J16" s="2">
+        <v>20</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="143">
   <si>
     <t>普通表模板</t>
   </si>
@@ -133,7 +133,7 @@
     <t>参数表模板</t>
   </si>
   <si>
-    <t>测试下常量生成</t>
+    <t>测试常量生成</t>
   </si>
   <si>
     <t>options</t>
@@ -166,7 +166,7 @@
     <t>baseCritRate</t>
   </si>
   <si>
-    <t>默认暴击值</t>
+    <t>默认暴击率</t>
   </si>
   <si>
     <t>测试参数表合并</t>
@@ -181,7 +181,7 @@
     <t>baseCritRate2</t>
   </si>
   <si>
-    <t>默认暴击值2</t>
+    <t>默认暴击率2</t>
   </si>
   <si>
     <t>有常量名的数据不可删</t>
@@ -235,7 +235,7 @@
     </r>
   </si>
   <si>
-    <t>bornPos</t>
+    <t>spawnPos</t>
   </si>
   <si>
     <t>场景id</t>
@@ -279,30 +279,25 @@
     <t>[50, 0, 50]</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>dojo</t>
-    </r>
-  </si>
-  <si>
     <t>试炼武馆</t>
   </si>
   <si>
     <t>{x: 1, y:1, z: 1}</t>
   </si>
   <si>
-    <t>测试枚举生成</t>
+    <t>测试List合并</t>
   </si>
   <si>
     <t>Element列可以不配置类型</t>
   </si>
   <si>
+    <t>C {i18n: true}</t>
+  </si>
+  <si>
     <t>C {isTuple: true}</t>
+  </si>
+  <si>
+    <t>ItemType</t>
   </si>
   <si>
     <r>
@@ -355,9 +350,6 @@
     </r>
   </si>
   <si>
-    <t>enumName</t>
-  </si>
-  <si>
     <t>jumpList</t>
   </si>
   <si>
@@ -390,6 +382,9 @@
     </r>
   </si>
   <si>
+    <t>物品类型</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -423,22 +418,25 @@
     </r>
   </si>
   <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>测试List合并</t>
+    <t>跳转列表</t>
+  </si>
+  <si>
+    <t>跳转1</t>
+  </si>
+  <si>
+    <t>跳转2</t>
+  </si>
+  <si>
+    <t>跳转3</t>
+  </si>
+  <si>
+    <t>测试字典合并</t>
   </si>
   <si>
     <t>跳表1</t>
   </si>
   <si>
     <t>跳表2</t>
-  </si>
-  <si>
-    <t>跳表3</t>
-  </si>
-  <si>
-    <t>测试字典合并</t>
   </si>
   <si>
     <r>
@@ -452,17 +450,10 @@
     </r>
   </si>
   <si>
-    <t>firstItemId</t>
-  </si>
-  <si>
     <t>linker_101</t>
   </si>
   <si>
     <t>linker_102</t>
-  </si>
-  <si>
-    <t>hello
-world</t>
   </si>
   <si>
     <t>{1 : linker_101 }</t>
@@ -497,10 +488,16 @@
     <t>测试表格继承</t>
   </si>
   <si>
+    <t>enumName</t>
+  </si>
+  <si>
     <t>equipLv</t>
   </si>
   <si>
     <t>flags</t>
+  </si>
+  <si>
+    <t>枚举名</t>
   </si>
   <si>
     <t>装备lv</t>
@@ -1814,14 +1811,13 @@
         <v>21</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" ht="15.6" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
+    <row r="2" ht="15.6" spans="2:5">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2089,8 +2085,10 @@
   <dimension ref="A7:F17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="5" width="10.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.4444444444444" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6666666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5555555555556" style="2" customWidth="1"/>
+    <col min="3" max="5" width="10.6666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.7777777777778" style="2" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2223,20 +2221,17 @@
       <c r="A17" s="2">
         <v>8001</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D17" s="2">
         <v>20</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2252,8 +2247,9 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.77777777777778" style="1" customWidth="1"/>
-    <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="4" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5555555555556" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
     <col min="7" max="9" width="12.6666666666667" style="1" customWidth="1"/>
     <col min="10" max="10" width="21.2222222222222" style="1" customWidth="1"/>
@@ -2261,16 +2257,40 @@
     <col min="13" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:10">
-      <c r="E1" s="1" t="s">
+    <row r="1" ht="15.6" spans="6:10">
+      <c r="F1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" ht="15.6" spans="6:11">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="6:11">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="6:11">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" ht="15.6" spans="1:12">
       <c r="A11" s="2" t="s">
@@ -2283,9 +2303,11 @@
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
@@ -2309,19 +2331,19 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>42</v>
@@ -2333,26 +2355,26 @@
         <v>42</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" ht="15.6" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>73</v>
@@ -2408,13 +2430,13 @@
         <v>89</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" ht="31.2" spans="1:12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" ht="15.6" spans="1:12">
       <c r="A15" s="2">
         <v>10001</v>
       </c>
@@ -2424,22 +2446,20 @@
       <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>90</v>
+      <c r="D15" s="2">
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" s="4" t="s">
         <v>94</v>
       </c>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
         <v>95</v>
@@ -2456,12 +2476,14 @@
         <v>1</v>
       </c>
       <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
         <v>0</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
         <v>98</v>
@@ -2487,28 +2509,27 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="4" width="9.33333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="9" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.22222222222222" customWidth="1"/>
-    <col min="11" max="11" width="11.2222222222222" customWidth="1"/>
+    <col min="1" max="2" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="5" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.2222222222222" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="1" customWidth="1"/>
+    <col min="8" max="10" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.22222222222222" customWidth="1"/>
+    <col min="12" max="12" width="11.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" ht="15.6" spans="10:17">
-      <c r="J4" s="2"/>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="11:18">
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -2516,9 +2537,9 @@
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="15.6" spans="10:17">
-      <c r="J5" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" ht="15.6" spans="11:18">
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -2526,9 +2547,9 @@
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="15.6" spans="10:17">
-      <c r="J6" s="2"/>
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" ht="15.6" spans="11:18">
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -2536,9 +2557,9 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-    </row>
-    <row r="7" ht="15.6" spans="10:17">
-      <c r="J7" s="2"/>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" ht="15.6" spans="11:18">
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -2546,9 +2567,9 @@
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="15.6" spans="10:17">
-      <c r="J8" s="2"/>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" ht="15.6" spans="11:18">
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -2556,9 +2577,9 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="15.6" spans="10:17">
-      <c r="J9" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" ht="15.6" spans="11:18">
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -2566,9 +2587,9 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-    </row>
-    <row r="10" ht="15.6" spans="10:17">
-      <c r="J10" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" ht="15.6" spans="11:18">
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -2576,8 +2597,9 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:17">
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:18">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -2588,14 +2610,14 @@
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>3</v>
@@ -2604,39 +2626,42 @@
         <v>3</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:17">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:18">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>42</v>
@@ -2645,60 +2670,66 @@
         <v>42</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:17">
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:18">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="F13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:17">
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:18">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
@@ -2715,87 +2746,104 @@
         <v>84</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="K14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-    </row>
-    <row r="15" ht="15.6" spans="1:14">
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:15">
       <c r="A15" s="2">
         <v>11001</v>
       </c>
       <c r="B15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>107</v>
+      <c r="D15" s="2">
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="2">
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
         <v>10</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-    </row>
-    <row r="16" ht="15.6" spans="1:14">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:15">
       <c r="A16" s="2">
         <v>11002</v>
       </c>
       <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
         <v>1</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
         <v>0</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2">
+      <c r="H16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2">
         <v>20</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2821,15 +2869,15 @@
   <sheetData>
     <row r="4" spans="5:6">
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="5:5">
       <c r="E5" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" ht="15.6" spans="1:8">
@@ -2846,10 +2894,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2859,47 +2907,47 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" ht="15.6" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:8">
@@ -2907,25 +2955,25 @@
         <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:8">
@@ -2933,13 +2981,13 @@
         <v>10001</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2">
         <v>1e-5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>17</v>
@@ -2959,10 +3007,10 @@
         <v>1e-5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -2983,13 +3031,13 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" ht="15.6" spans="1:8">
@@ -3003,16 +3051,16 @@
         <v>1e-5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" ht="15.6" spans="1:8">
@@ -3026,13 +3074,13 @@
         <v>1e-5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:8">
@@ -3046,16 +3094,16 @@
         <v>1e-5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" ht="15.6" spans="1:8">
@@ -3070,13 +3118,13 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" ht="15.6" spans="1:8">
@@ -3090,13 +3138,13 @@
         <v>1e-5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" ht="15.6" spans="1:8">
@@ -3111,13 +3159,13 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" ht="15.6" spans="1:8">
@@ -3132,13 +3180,13 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
+++ b/csharp/Wjybxx.BigCatTool.Tests/res/test.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Item.Base" sheetId="4" r:id="rId5"/>
     <sheet name="Item.Equip" sheetId="6" r:id="rId6"/>
     <sheet name="Test" sheetId="5" r:id="rId7"/>
+    <sheet name="_Lang" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="170">
   <si>
     <t>普通表模板</t>
   </si>
@@ -294,6 +295,9 @@
     <t>C {i18n: true}</t>
   </si>
   <si>
+    <t>C {intern: true}</t>
+  </si>
+  <si>
     <t>C {isTuple: true}</t>
   </si>
   <si>
@@ -350,6 +354,9 @@
     </r>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>jumpList</t>
   </si>
   <si>
@@ -418,6 +425,9 @@
     </r>
   </si>
   <si>
+    <t>图标路径</t>
+  </si>
+  <si>
     <t>跳转列表</t>
   </si>
   <si>
@@ -450,6 +460,9 @@
     </r>
   </si>
   <si>
+    <t>10001.png</t>
+  </si>
+  <si>
     <t>linker_101</t>
   </si>
   <si>
@@ -473,6 +486,9 @@
     </r>
   </si>
   <si>
+    <t>10002.png</t>
+  </si>
+  <si>
     <t>linker_201</t>
   </si>
   <si>
@@ -485,6 +501,9 @@
     <t>{2 : linker_202 }</t>
   </si>
   <si>
+    <t>3号物品</t>
+  </si>
+  <si>
     <t>测试表格继承</t>
   </si>
   <si>
@@ -506,12 +525,12 @@
     <t>测试Flags</t>
   </si>
   <si>
+    <t>firstEquipId</t>
+  </si>
+  <si>
     <t>1号装备</t>
   </si>
   <si>
-    <t>firstEquipId</t>
-  </si>
-  <si>
     <t>1 | 32 | 64</t>
   </si>
   <si>
@@ -606,6 +625,189 @@
   </si>
   <si>
     <t>ani_30010</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>C</t>
+    </r>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>srcText</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>destText</t>
+    </r>
+  </si>
+  <si>
+    <t>ssti</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>单元格坐标</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文本id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原始文本</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>翻译后或池化的文本</t>
+    </r>
+  </si>
+  <si>
+    <t>共享字符串表索引</t>
+  </si>
+  <si>
+    <t>文本内容</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>...</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>the first item</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>item_10001_icon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>the second item</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>item_10002_icon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10001.png</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>item_10003_icon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10002.png</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -982,12 +1184,92 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1114,7 +1396,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1126,34 +1408,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1238,14 +1520,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -1605,183 +1911,183 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3796296296296" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.8796296296296" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.8796296296296" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="12.75" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.3796296296296" style="10" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="10" customWidth="1"/>
+    <col min="4" max="4" width="14.8796296296296" style="10" customWidth="1"/>
+    <col min="5" max="5" width="15.8796296296296" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="2" ht="15.6" spans="1:5">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" ht="15.6" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" ht="15.6" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" ht="15.6" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" ht="15.6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" ht="15.6" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" ht="15.6" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" ht="15.6" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" ht="15.6" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" ht="15.6" spans="1:5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" ht="15.6" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" ht="15.6" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" ht="15.6" spans="1:5">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:5">
-      <c r="A15" s="2">
+      <c r="A15" s="5">
         <v>10001</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="5">
         <v>20001</v>
       </c>
-      <c r="C15" s="2" t="b">
+      <c r="C15" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:5">
-      <c r="A16" s="2">
+      <c r="A16" s="5">
         <v>10002</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="5">
         <v>20002</v>
       </c>
-      <c r="C16" s="2" t="b">
+      <c r="C16" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1798,135 +2104,135 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="19.7777777777778" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.66666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.66666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19.7777777777778" style="10" customWidth="1"/>
+    <col min="2" max="2" width="6.66666666666667" style="10" customWidth="1"/>
+    <col min="3" max="3" width="19.7777777777778" style="10" customWidth="1"/>
+    <col min="4" max="4" width="6.66666666666667" style="10" customWidth="1"/>
+    <col min="5" max="5" width="11.8888888888889" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="2" ht="15.6" spans="2:5">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" ht="15.6" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" ht="15.6" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" ht="15.6" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" ht="15.6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" ht="15.6" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" ht="15.6" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" ht="15.6" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" ht="15.6" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" ht="15.6" spans="1:5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="15.6" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="5">
         <v>0.8</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="5">
         <v>0.15</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1943,133 +2249,133 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="11.8888888888889" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.66666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.66666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.8888888888889" style="10" customWidth="1"/>
+    <col min="2" max="2" width="6.66666666666667" style="10" customWidth="1"/>
+    <col min="3" max="3" width="19.7777777777778" style="10" customWidth="1"/>
+    <col min="4" max="4" width="6.66666666666667" style="10" customWidth="1"/>
+    <col min="5" max="5" width="11.8888888888889" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="2" ht="15.6" spans="1:5">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" ht="15.6" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" ht="15.6" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" ht="15.6" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" ht="15.6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" ht="15.6" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" ht="15.6" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" ht="15.6" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" ht="15.6" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" ht="15.6" spans="1:5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="15.6" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="5">
         <v>0.8</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="5">
         <v>0.15</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2085,152 +2391,152 @@
   <dimension ref="A7:F17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="10.6666666666667" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.5555555555556" style="2" customWidth="1"/>
-    <col min="3" max="5" width="10.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.7777777777778" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.6666666666667" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6666666666667" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.5555555555556" style="5" customWidth="1"/>
+    <col min="3" max="5" width="10.6666666666667" style="5" customWidth="1"/>
+    <col min="6" max="6" width="19.7777777777778" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.6666666666667" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="7" spans="2:6">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="2">
+      <c r="A15" s="5">
         <v>1001</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="2">
+      <c r="A16" s="5">
         <v>1002</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="5">
         <v>2</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="2">
+      <c r="A17" s="5">
         <v>8001</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="5">
         <v>20</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2243,262 +2549,474 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.77777777777778" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.33333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5555555555556" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="9" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.2222222222222" style="1" customWidth="1"/>
-    <col min="11" max="12" width="17" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="7.77777777777778" style="10" customWidth="1"/>
+    <col min="2" max="2" width="10.7777777777778" style="10" customWidth="1"/>
+    <col min="3" max="4" width="9.33333333333333" style="10" customWidth="1"/>
+    <col min="5" max="5" width="14.5555555555556" style="10" customWidth="1"/>
+    <col min="6" max="6" width="18.3333333333333" style="10" customWidth="1"/>
+    <col min="7" max="7" width="19" style="10" customWidth="1"/>
+    <col min="8" max="10" width="12.6666666666667" style="10" customWidth="1"/>
+    <col min="11" max="11" width="21.2222222222222" style="10" customWidth="1"/>
+    <col min="12" max="13" width="17" style="10" customWidth="1"/>
+    <col min="14" max="16382" width="8.88888888888889" style="10"/>
+    <col min="16384" max="16384" width="8.88888888888889" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="6:10">
-      <c r="F1" s="2" t="s">
+    <row r="1" ht="15.6" spans="7:11">
+      <c r="G1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" ht="15.6" spans="6:11">
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="15.6" spans="6:11">
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" ht="15.6" spans="6:11">
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:12">
-      <c r="A11" s="2" t="s">
+    <row r="6" ht="15.6" spans="6:6">
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" ht="15.6" spans="6:6">
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" ht="15.6" spans="6:12">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" ht="15.6" spans="6:12">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:13">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:13">
+      <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:12">
-      <c r="A12" s="2" t="s">
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:13">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="F12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:12">
-      <c r="A13" s="2" t="s">
+      <c r="K12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:13">
+      <c r="A13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="F13" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="G13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="H13" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="I13" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="J13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" ht="15.6" spans="1:12">
-      <c r="A14" s="2" t="s">
+      <c r="L13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="M13" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="14" ht="15.6" spans="1:13">
+      <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="G14" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="H14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="I14" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="J14" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="15" ht="15.6" spans="1:12">
-      <c r="A15" s="2">
+      <c r="K14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" ht="15.6" spans="1:13">
+      <c r="A15" s="5">
         <v>10001</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="5">
         <v>1</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="5">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="F15" s="5" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="16" ht="15.6" spans="1:12">
-      <c r="A16" s="2">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:13">
+      <c r="A16" s="5">
         <v>10002</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="5">
         <v>1</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="5">
         <v>1</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="5">
         <v>0</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>101</v>
       </c>
+      <c r="F16" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" ht="15.6" spans="1:13">
+      <c r="A17" s="5">
+        <v>10003</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" ht="15.6" spans="1:13">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" ht="15.6" spans="1:13">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" ht="15.6" spans="1:13">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" ht="15.6" spans="1:13">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" ht="15.6" spans="1:13">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" ht="15.6" spans="1:13">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" ht="15.6" spans="1:13">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+    </row>
+    <row r="25" ht="15.6" spans="1:13">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+    </row>
+    <row r="26" ht="15.6" spans="1:13">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" ht="15.6" spans="1:13">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2509,341 +3027,401 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="14.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="5" width="9.33333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.2222222222222" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19" style="1" customWidth="1"/>
-    <col min="8" max="10" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.22222222222222" customWidth="1"/>
-    <col min="12" max="12" width="11.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.2222222222222" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14.1111111111111" style="10" customWidth="1"/>
+    <col min="4" max="6" width="9.33333333333333" style="10" customWidth="1"/>
+    <col min="7" max="7" width="18.3333333333333" style="10" customWidth="1"/>
+    <col min="8" max="8" width="19" style="10" customWidth="1"/>
+    <col min="9" max="11" width="12.6666666666667" style="10" customWidth="1"/>
+    <col min="12" max="12" width="9.22222222222222" customWidth="1"/>
+    <col min="13" max="13" width="11.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="12:19">
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" ht="15.6" spans="12:19">
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" ht="15.6" spans="7:19">
+      <c r="G6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" ht="15.6" spans="7:19">
+      <c r="G7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" ht="15.6" spans="7:19">
+      <c r="G8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+    </row>
+    <row r="9" ht="15.6" spans="7:19">
+      <c r="G9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+    </row>
+    <row r="10" ht="15.6" spans="7:19">
+      <c r="G10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:19">
+      <c r="A11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:19">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:19">
+      <c r="A13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:19">
+      <c r="A14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:16">
+      <c r="A15" s="5">
+        <v>11001</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5">
+        <v>10</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:16">
+      <c r="A16" s="5">
+        <v>11002</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" ht="15.6" spans="11:18">
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-    </row>
-    <row r="5" ht="15.6" spans="11:18">
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-    </row>
-    <row r="6" ht="15.6" spans="11:18">
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-    </row>
-    <row r="7" ht="15.6" spans="11:18">
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" ht="15.6" spans="11:18">
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-    </row>
-    <row r="9" ht="15.6" spans="11:18">
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-    </row>
-    <row r="10" ht="15.6" spans="11:18">
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:18">
-      <c r="A11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-    </row>
-    <row r="12" ht="15.6" spans="1:18">
-      <c r="A12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-    </row>
-    <row r="13" ht="15.6" spans="1:18">
-      <c r="A13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="J16" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-    </row>
-    <row r="14" ht="15.6" spans="1:18">
-      <c r="A14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-    </row>
-    <row r="15" ht="15.6" spans="1:15">
-      <c r="A15" s="2">
-        <v>11001</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2">
-        <v>10</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" ht="15.6" spans="1:15">
-      <c r="A16" s="2">
-        <v>11002</v>
-      </c>
-      <c r="B16" s="2">
-        <v>2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2">
+      <c r="K16" s="5"/>
+      <c r="L16" s="5">
         <v>20</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="M16" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" ht="15.6" spans="7:7">
+      <c r="G17" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" ht="15.6" spans="7:7">
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" ht="15.6" spans="7:7">
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" ht="15.6" spans="7:7">
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" ht="15.6" spans="7:7">
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" ht="15.6" spans="7:7">
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" ht="15.6" spans="7:7">
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" ht="15.6" spans="7:7">
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" ht="15.6" spans="7:7">
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" ht="15.6" spans="7:7">
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" ht="15.6" spans="7:7">
+      <c r="G27" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2857,336 +3435,336 @@
   <dimension ref="A4:H24"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="27" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.4444444444444" style="1" customWidth="1"/>
-    <col min="7" max="8" width="29" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="10"/>
+    <col min="2" max="2" width="27" style="10" customWidth="1"/>
+    <col min="3" max="3" width="28.6666666666667" style="10" customWidth="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="10" customWidth="1"/>
+    <col min="5" max="5" width="30.6666666666667" style="10" customWidth="1"/>
+    <col min="6" max="6" width="18.4444444444444" style="10" customWidth="1"/>
+    <col min="7" max="8" width="29" style="10" customWidth="1"/>
+    <col min="9" max="16384" width="8.88888888888889" style="10"/>
   </cols>
   <sheetData>
     <row r="4" spans="5:6">
-      <c r="E4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>114</v>
+      <c r="E4" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="5:5">
-      <c r="E5" s="1" t="s">
-        <v>115</v>
+      <c r="E5" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="15.6" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="E11" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" ht="15.6" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="B12" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" ht="15.6" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="A13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>125</v>
       </c>
+      <c r="C13" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="14" ht="15.6" spans="1:8">
-      <c r="A14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>129</v>
+      <c r="A14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="15" ht="15.6" spans="1:8">
-      <c r="A15" s="2">
+      <c r="A15" s="5">
         <v>10001</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="5">
         <v>1e-5</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="E15" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:8">
-      <c r="A16" s="2">
+      <c r="A16" s="5">
         <v>10002</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="11">
         <v>0.1</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="5">
         <v>1e-5</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="D16" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:8">
-      <c r="A17" s="2">
+      <c r="A17" s="5">
         <v>10003</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="11">
         <v>0.1</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="5">
         <v>1e-5</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>133</v>
+      <c r="D17" s="5"/>
+      <c r="E17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="18" ht="15.6" spans="1:8">
-      <c r="A18" s="2">
+      <c r="A18" s="5">
         <v>10004</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="11">
         <v>0.1</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="5">
         <v>1e-5</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>135</v>
+      <c r="D18" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" ht="15.6" spans="1:8">
-      <c r="A19" s="2">
+      <c r="A19" s="5">
         <v>10005</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="5">
         <v>0.1</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="5">
         <v>1e-5</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>136</v>
+      <c r="E19" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:8">
-      <c r="A20" s="2">
+      <c r="A20" s="5">
         <v>10006</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="5">
         <v>0.1</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="5">
         <v>1e-5</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>138</v>
+      <c r="G20" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="21" ht="15.6" spans="1:8">
-      <c r="A21" s="2">
+      <c r="A21" s="5">
         <v>10007</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="5">
         <v>0.1</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="5">
         <v>1e-5</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>139</v>
+      <c r="D21" s="5"/>
+      <c r="E21" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="22" ht="15.6" spans="1:8">
-      <c r="A22" s="2">
+      <c r="A22" s="5">
         <v>10008</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="5">
         <v>0.1</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="5">
         <v>1e-5</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>140</v>
+      <c r="E22" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="23" ht="15.6" spans="1:8">
-      <c r="A23" s="2">
+      <c r="A23" s="5">
         <v>10009</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="5">
         <v>0.1</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="5">
         <v>1e-5</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>141</v>
+      <c r="D23" s="5"/>
+      <c r="E23" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="24" ht="15.6" spans="1:8">
-      <c r="A24" s="2">
+      <c r="A24" s="5">
         <v>10010</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="5">
         <v>0.1</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="5">
         <v>1e-5</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>142</v>
+      <c r="D24" s="5"/>
+      <c r="E24" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3194,4 +3772,357 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A4:M22"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="7.77777777777778" customWidth="1"/>
+    <col min="2" max="2" width="10.7777777777778" customWidth="1"/>
+    <col min="3" max="4" width="9.33333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.77777777777778" customWidth="1"/>
+    <col min="6" max="6" width="10.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="18.5555555555556" customWidth="1"/>
+    <col min="8" max="8" width="9.33333333333333" customWidth="1"/>
+    <col min="9" max="9" width="14.5555555555556" customWidth="1"/>
+    <col min="10" max="10" width="20.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="18.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="7.44444444444444" customWidth="1"/>
+    <col min="13" max="13" width="9.33333333333333" customWidth="1"/>
+    <col min="14" max="14" width="7.22222222222222" customWidth="1"/>
+    <col min="15" max="15" width="17.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" ht="15.6" spans="3:8">
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" ht="15.6" spans="3:8">
+      <c r="C5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="15.6" spans="3:8">
+      <c r="C6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6" spans="3:8">
+      <c r="C7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" ht="15.6" spans="3:8">
+      <c r="C8" s="4">
+        <v>10001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>101</v>
+      </c>
+      <c r="H8" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" ht="15.6" spans="3:8">
+      <c r="C9" s="4">
+        <v>10002</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>102</v>
+      </c>
+      <c r="H9" s="6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" ht="15.6" spans="3:8">
+      <c r="C10" s="4">
+        <v>10003</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>103</v>
+      </c>
+      <c r="H10" s="6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" ht="15.6" spans="3:8">
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="9"/>
+    </row>
+    <row r="12" ht="15.6" spans="5:5">
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" ht="15.6" spans="5:5">
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" ht="15.6" spans="5:5">
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" ht="15.6" spans="5:13">
+      <c r="E15" s="1"/>
+      <c r="F15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" spans="1:13">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="E16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" ht="15.6" spans="5:13">
+      <c r="E17" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" ht="15.6" spans="5:13">
+      <c r="E18" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" ht="15.6" spans="5:13">
+      <c r="E19" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" ht="15.6" spans="5:13">
+      <c r="E20" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="5">
+        <v>104</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="6">
+        <v>3</v>
+      </c>
+      <c r="L20" s="4">
+        <v>2</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" ht="15.6" spans="5:13">
+      <c r="E21" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F21" s="5">
+        <v>105</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="6">
+        <v>4</v>
+      </c>
+      <c r="L21" s="4">
+        <v>3</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" ht="15.6" spans="5:13">
+      <c r="E22" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="8">
+        <v>106</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="9">
+        <v>4</v>
+      </c>
+      <c r="L22" s="7">
+        <v>4</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>